--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.7257137700507</v>
+        <v>9.86792848763324</v>
       </c>
       <c r="D2" t="n">
-        <v>29.28029776258815</v>
+        <v>4.758048386420574</v>
       </c>
       <c r="E2" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F2" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.19679570899489</v>
+        <v>7.34447930271167</v>
       </c>
       <c r="D3" t="n">
-        <v>19.36571033191204</v>
+        <v>3.146927928935707</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F3" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.47211961075728</v>
+        <v>6.251719436748059</v>
       </c>
       <c r="D4" t="n">
-        <v>11.86333520889862</v>
+        <v>1.927791971446026</v>
       </c>
       <c r="E4" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F4" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.75256968259239</v>
+        <v>3.534792573421264</v>
       </c>
       <c r="D5" t="n">
-        <v>13.61735763944224</v>
+        <v>2.212820616409365</v>
       </c>
       <c r="E5" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F5" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.16390842530927</v>
+        <v>8.476635119112757</v>
       </c>
       <c r="D6" t="n">
-        <v>28.6819978259149</v>
+        <v>4.660824646711171</v>
       </c>
       <c r="E6" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F6" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.94726058819345</v>
+        <v>2.916429845581436</v>
       </c>
       <c r="D7" t="n">
-        <v>22.28650289734575</v>
+        <v>3.621556720818684</v>
       </c>
       <c r="E7" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F7" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.57409090953315</v>
+        <v>2.368289772799137</v>
       </c>
       <c r="D8" t="n">
-        <v>10.63254428138544</v>
+        <v>1.727788445725134</v>
       </c>
       <c r="E8" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F8" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.99517788937112</v>
+        <v>5.849216407022808</v>
       </c>
       <c r="D9" t="n">
-        <v>13.62595319918254</v>
+        <v>2.214217394867164</v>
       </c>
       <c r="E9" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F9" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69433687143614</v>
+        <v>7.262829741608374</v>
       </c>
       <c r="D10" t="n">
-        <v>17.29680590744309</v>
+        <v>2.810730959959503</v>
       </c>
       <c r="E10" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F10" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.17918674071599</v>
+        <v>6.691617845366348</v>
       </c>
       <c r="D11" t="n">
-        <v>33.3216941501325</v>
+        <v>5.414775299396531</v>
       </c>
       <c r="E11" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F11" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.24429110674201</v>
+        <v>4.589697304845576</v>
       </c>
       <c r="D12" t="n">
-        <v>28.06722557091703</v>
+        <v>4.560924155274018</v>
       </c>
       <c r="E12" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F12" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.24510812876786</v>
+        <v>4.914830070924777</v>
       </c>
       <c r="D13" t="n">
-        <v>28.05856076786628</v>
+        <v>4.55951612477827</v>
       </c>
       <c r="E13" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F13" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>66.42813998348872</v>
+        <v>10.79457274731692</v>
       </c>
       <c r="D14" t="n">
-        <v>44.34474890217959</v>
+        <v>7.206021696604183</v>
       </c>
       <c r="E14" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F14" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>76.0347040048006</v>
+        <v>12.3556394007801</v>
       </c>
       <c r="D15" t="n">
-        <v>57.8162864004195</v>
+        <v>9.395146540068168</v>
       </c>
       <c r="E15" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F15" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.64789580632068</v>
+        <v>7.74278306852711</v>
       </c>
       <c r="D16" t="n">
-        <v>39.96759686868948</v>
+        <v>6.49473449116204</v>
       </c>
       <c r="E16" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F16" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>57.21205811589276</v>
+        <v>9.296959443832574</v>
       </c>
       <c r="D17" t="n">
-        <v>40.74381658533969</v>
+        <v>6.620870195117699</v>
       </c>
       <c r="E17" t="n">
-        <v>16.96399342130698</v>
+        <v>2.756648930962384</v>
       </c>
       <c r="F17" t="n">
-        <v>12.95273690768889</v>
+        <v>2.104819747499444</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
